--- a/TestData/Register_TestData.xlsx
+++ b/TestData/Register_TestData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="29">
   <si>
     <t xml:space="preserve">Scenario</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t xml:space="preserve">KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phone Already Registered</t>
   </si>
 </sst>
 </file>
@@ -212,7 +215,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.19"/>
@@ -397,6 +400,32 @@
         <v>17</v>
       </c>
     </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>965321152</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
